--- a/costTracker/social-media-tracker.xlsx
+++ b/costTracker/social-media-tracker.xlsx
@@ -7323,7 +7323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C3:L21"/>
+  <dimension ref="C3:L23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="47.1640625" customWidth="1" style="22" min="6" max="6"/>
@@ -8179,6 +8179,94 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="n">
+        <v>19</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>pillars-4k-batch</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Social Pillars — 36 4K masters (pillars 1,2,4,5,6,7)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Higgsfield: 36 nano_banana_pro 1:1 @ 4k masters (4096x4096, 4cr ea) for the 49-post V4 plan, one failed and re-rolled. Reframed locally to 180 platform exports (4:5 / 16:9 / 9:16 / 2:3 / 1:1) via scripts/social/reframe.py + export_all.py, logo watermarked. Captions written for all 7 pillars. Pillar 3 (teacher) deliberately not generated — real photos required.</t>
+        </is>
+      </c>
+      <c r="G22" s="27" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>n/a (images x36 + 180 exports)</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>144</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>nano_banana_pro 4k</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>riwaq_social_media_package_v4.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="n">
+        <v>20</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4df3aba8</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Wudu Together (video, pillar 1.5)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Higgsfield: reused pillar 1.5 4K master reframed to 9:16 as start frame (0cr) + 1 nano_banana_pro 2k drying still (2cr) + 3 veo3_1 fast 8s clips (2 kept, 1 failed and re-rolled). Silent by design — VAD-confirmed no speech, ambient water/fabric only. Local assembly: 5s+5s trim, Pillow on-screen text at two beats per brief, warm fade-out.</t>
+        </is>
+      </c>
+      <c r="G23" s="27" t="n">
+        <v>46245</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0:10</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>68</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>nano_banana_pro + veo3_1 fast</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Pillers/Wudu Together.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/costTracker/social-media-tracker.xlsx
+++ b/costTracker/social-media-tracker.xlsx
@@ -7323,7 +7323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C3:L23"/>
+  <dimension ref="C3:L24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="47.1640625" customWidth="1" style="22" min="6" max="6"/>
@@ -8267,6 +8267,50 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="C24" t="n">
+        <v>21</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0022</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Lā ḥawla wa lā quwwata illā billāh</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Higgsfield: 8 nano_banana_pro stills (master + 7 scenes) + 9 veo-3-1-fast clips (8 used, 1 sunrise re-rolled after v1 clipped to white) + seed_audio Emmett VO. v2 rebuild: all 8 beats real motion, one continuous read. All veo clip audio discarded (6 of 9 returned a music bed); soundtrack built locally = VO + Apple-DLS piano + rain ambience. Arabic dua on 6 Pillow cards because TTS could not pronounce 'quwwata' in 7 attempts.</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="n">
+        <v>46245</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0:58</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>231</v>
+      </c>
+      <c r="J24" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>nano_banana_pro + veo-3-1-fast + seed_audio</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>productions/0022-la-hawla/00-REQUEST.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/costTracker/social-media-tracker.xlsx
+++ b/costTracker/social-media-tracker.xlsx
@@ -7323,7 +7323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C3:L24"/>
+  <dimension ref="C3:L25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="47.1640625" customWidth="1" style="22" min="6" max="6"/>
@@ -8311,6 +8311,50 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="C25" t="n">
+        <v>22</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Alif, Baa, Taa Adventure (Rhyme Series S2 #7)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Higgsfield: 7 nano_banana_pro stills (Johra.jpeg identity ref) + 8 veo-3-1-fast clips (7 used, Saa re-rolled because the finger count changed mid-clip) + seed_audio Juno spoken read at speech_rate 20. Style 7. Auditioned 3 voices: Daisy said 'Aleph', Gracie 'Aleaf', only Juno said 'Alif'. All 8 clips carried a music bed (-22..-27 dB) so all clip audio discarded; marimba bed rendered locally via new scripts/social/kidsmusic.m. Arabic letter cards Pillow-rendered.</t>
+        </is>
+      </c>
+      <c r="G25" s="27" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1:01</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>215</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>nano_banana_pro + veo-3-1-fast + seed_audio</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>productions/0024-alif-baa-taa-adventure/00-REQUEST.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/costTracker/social-media-tracker.xlsx
+++ b/costTracker/social-media-tracker.xlsx
@@ -7323,7 +7323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C3:L25"/>
+  <dimension ref="C3:L26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="47.1640625" customWidth="1" style="22" min="6" max="6"/>
@@ -8355,6 +8355,50 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="C26" t="n">
+        <v>23</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Allah Made Everything (image)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Higgsfield: nano_banana_pro 1:1 @ 4k (4096x4096) 3D-animated children's illustration, no text baked. A photoreal variant was also submitted and came back nsfw (false positive, not charged) — second time a photoreal-child prompt has tripped that filter while animated passes.</t>
+        </is>
+      </c>
+      <c r="G26" s="27" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>n/a (image)</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>nano_banana_pro 4k</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>productions/0026-allah-made-everything/00-REQUEST.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/costTracker/social-media-tracker.xlsx
+++ b/costTracker/social-media-tracker.xlsx
@@ -7323,7 +7323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C3:L26"/>
+  <dimension ref="C3:L27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="47.1640625" customWidth="1" style="22" min="6" max="6"/>
@@ -8399,6 +8399,50 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="C27" t="n">
+        <v>24</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0027</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Allah Made Everything (post image, 2 children)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Higgsfield: nano_banana_pro 1:1 @ 4k, premium preschool 3D register, no text generated. Title '🌎 ALLAH MADE EVERYTHING 🌿' and the brief's couplet composited locally with Pillow (work/compose.py); Apple Color Emoji only rasterises at 96px so emoji are drawn at 96 and scaled. Two masters shipped: titled post + clean textless. Style 5.</t>
+        </is>
+      </c>
+      <c r="G27" s="27" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>n/a (image x2)</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>nano_banana_pro 4k</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>productions/0027-allah-made-everything-post-image/00-REQUEST.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/costTracker/social-media-tracker.xlsx
+++ b/costTracker/social-media-tracker.xlsx
@@ -7323,7 +7323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C3:L27"/>
+  <dimension ref="C3:L28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="47.1640625" customWidth="1" style="22" min="6" max="6"/>
@@ -8443,6 +8443,50 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="C28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>0028</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Thank You, Allah (post image)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Higgsfield: nano_banana_pro 1:1 @ 4k, animated preschool register, no text generated. First production via the /riwaq-image-post skill: postkit.py wrote all 5 platform ratios + a textless master, type composited locally. Prompt asked for a clear lower-left corner so the logo had somewhere to sit — worked first try. White-heart emoji swapped for a blossom, invisible on a peach wall.</t>
+        </is>
+      </c>
+      <c r="G28" s="27" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>n/a (image x6)</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>nano_banana_pro 4k</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>productions/0028-thank-you-allah/00-REQUEST.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/costTracker/social-media-tracker.xlsx
+++ b/costTracker/social-media-tracker.xlsx
@@ -7323,7 +7323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C3:L28"/>
+  <dimension ref="C3:L29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="47.1640625" customWidth="1" style="22" min="6" max="6"/>
@@ -8487,6 +8487,50 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="C29" t="n">
+        <v>26</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0029</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Allah Loves When I Do Good (post image)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Higgsfield: nano_banana_pro 1:1 @ 4k, animated preschool register, no text generated, no re-roll needed. Two good deeds in frame (sharing half an orange, water for a kitten). Built with /riwaq-image-post. 16:9 and 2:3 needed crop retuning — 2:3 at the inherited bias cropped the second deed out entirely — so postkit.py gained a --override flag for per-image crop and type tuning.</t>
+        </is>
+      </c>
+      <c r="G29" s="27" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>n/a (image x6)</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>nano_banana_pro 4k</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>productions/0029-allah-loves-when-i-do-good/00-REQUEST.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/costTracker/social-media-tracker.xlsx
+++ b/costTracker/social-media-tracker.xlsx
@@ -7323,7 +7323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C3:L29"/>
+  <dimension ref="C3:L30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="47.1640625" customWidth="1" style="22" min="6" max="6"/>
@@ -8531,6 +8531,50 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="C30" t="n">
+        <v>27</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Bismillah Before I Begin (post image)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Higgsfield: nano_banana_pro 1:1 @ 4k, animated preschool register, no text generated (book cover pinned blank three ways), no re-roll. Everything in frame is pre-action: closed book, untouched milk, packed satchel, shoes by the door. Via /riwaq-image-post; crop biases set from this composition up front (subject sits right of centre) and the 16:9 couplet moved LEFT, opposite side to 0029.</t>
+        </is>
+      </c>
+      <c r="G30" s="27" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>n/a (image x6)</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>nano_banana_pro 4k</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>productions/0030-bismillah-before-i-begin/00-REQUEST.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/costTracker/social-media-tracker.xlsx
+++ b/costTracker/social-media-tracker.xlsx
@@ -7323,7 +7323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C3:L30"/>
+  <dimension ref="C3:L31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="47.1640625" customWidth="1" style="22" min="6" max="6"/>
@@ -8575,6 +8575,50 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="C31" t="n">
+        <v>28</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0031</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Alhamdulillah Every Day (post image)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Higgsfield: nano_banana_pro 1:1 @ 4k, animated preschool register, no text and no numbers generated, no re-roll. Deliberately separated from 0028 on three axes (morning vs evening, standing vs kneeling, daily-repeat vs count-your-blessings). Via /riwaq-image-post; 16:9 couplet moved down off the windowsill birds and the bird emoji swapped for a sunrise after failing the small-size contrast check.</t>
+        </is>
+      </c>
+      <c r="G31" s="27" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>n/a (image x6)</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>nano_banana_pro 4k</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>productions/0031-alhamdulillah-every-day/00-REQUEST.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/costTracker/social-media-tracker.xlsx
+++ b/costTracker/social-media-tracker.xlsx
@@ -7323,7 +7323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C3:L31"/>
+  <dimension ref="C3:L32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="47.1640625" customWidth="1" style="22" min="6" max="6"/>
@@ -8619,6 +8619,50 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="n">
+        <v>29</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0032</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SubhanAllah, Look Around! (post image)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Higgsfield: nano_banana_pro 1:1 @ 4k, animated preschool register, no text generated. Macro/close-up deliberately inverted from 0027's wide landscape (caught by checking INDEX.md before starting). First attempt returned nsfw — false positive on 'lying propped on her elbows', NOT charged; rewriting the posture as crouching passed. No ratio retune needed, first time. Via /riwaq-image-post.</t>
+        </is>
+      </c>
+      <c r="G32" s="27" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>n/a (image x6)</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>nano_banana_pro 4k</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>productions/0032-subhanallah-look-around/00-REQUEST.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/costTracker/social-media-tracker.xlsx
+++ b/costTracker/social-media-tracker.xlsx
@@ -7323,7 +7323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C3:L32"/>
+  <dimension ref="C3:L33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="47.1640625" customWidth="1" style="22" min="6" max="6"/>
@@ -8663,6 +8663,50 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="C33" t="n">
+        <v>30</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0033</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Alif Baa Taa rhyme — 10s SUNG test</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Higgsfield: nano_banana_pro 2k master still (Johra animated, recurring character ref) + 1 veo-3-1-fast 8s clip with lyrics pinned as SUNG. PROVES VEO CAN SING: 18.1-semitone pitch spread, 29 held notes &gt;=80ms, 86% voiced. Character holds across all 8s. Defect: sings 'Elef-ba-ta-ta' instead of 'Alif, Baa, Taa' — same Aleph failure as 0024's voice audition. Test succeeded, video not publishable. One still re-rolled (came back 16:9 letterboxed in a 9:16 canvas); one nsfw false positive on 'full body' + child, not charged.</t>
+        </is>
+      </c>
+      <c r="G33" s="27" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0:10</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>26</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>nano_banana_pro 2k + veo-3-1-fast</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>productions/0033-alif-baa-taa-rhyme-10s-sung-test/00-REQUEST.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/costTracker/social-media-tracker.xlsx
+++ b/costTracker/social-media-tracker.xlsx
@@ -7323,7 +7323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C3:L33"/>
+  <dimension ref="C3:L34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="47.1640625" customWidth="1" style="22" min="6" max="6"/>
@@ -8707,6 +8707,50 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="C34" t="n">
+        <v>31</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0034</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Alif CoComelon 10s (Gemini Omni Flash)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Higgsfield gemini_omni (Gemini Omni Flash): ONE 10s clip, native audio, 9:16, reusing 0033's Johra master still as image reference (no new still cost). Honoured the written cut list exactly — scene cuts measured at 3.50 and 6.54s, fixing 0033's single-static-shot rejection. Pronunciation FIXED to 'Ahlif' by spelling the lyric phonetically. Defect: rendered garbled pseudo-text 'UXely' from 8.4s despite three prohibitions; covered locally with the Arabic Alif card. Open: pitch spread 5.7 semitones vs veo's 18.1 — may be chant not song.</t>
+        </is>
+      </c>
+      <c r="G34" s="27" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0:10</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>30</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>gemini_omni (Omni Flash)</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>productions/0034-alif-cocomelon-10s-omni-flash/00-REQUEST.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/costTracker/social-media-tracker.xlsx
+++ b/costTracker/social-media-tracker.xlsx
@@ -8723,7 +8723,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Higgsfield gemini_omni (Gemini Omni Flash): ONE 10s clip, native audio, 9:16, reusing 0033's Johra master still as image reference (no new still cost). Honoured the written cut list exactly — scene cuts measured at 3.50 and 6.54s, fixing 0033's single-static-shot rejection. Pronunciation FIXED to 'Ahlif' by spelling the lyric phonetically. Defect: rendered garbled pseudo-text 'UXely' from 8.4s despite three prohibitions; covered locally with the Arabic Alif card. Open: pitch spread 5.7 semitones vs veo's 18.1 — may be chant not song.</t>
+          <t>Higgsfield gemini_omni (Gemini Omni Flash): ONE 10s clip, native audio, 9:16, reusing 0033's Johra master still as image reference (no new still cost). Honoured the written cut list exactly — scene cuts measured at 3.50 and 6.54s, fixing 0033's single-static-shot rejection. Pronunciation FIXED to 'Ahlif' by spelling the lyric phonetically. Defect: rendered garbled pseudo-text 'UXely' from 8.4s despite three prohibitions; covered locally with the Arabic Alif card. Open: pitch spread 5.7 semitones vs veo's 18.1 — may be chant not song. THREE generations total (90cr): v1 picture approved by user; v2 'AL-if' and v3 plain 'Alif' both render as 'Elif' and v3 also lost a cut. Pronunciation route closed — needs a supplied sung vocal.</t>
         </is>
       </c>
       <c r="G34" s="27" t="n">
@@ -8735,10 +8735,10 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="J34" t="n">
-        <v>0.99</v>
+        <v>2.97</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>

--- a/costTracker/social-media-tracker.xlsx
+++ b/costTracker/social-media-tracker.xlsx
@@ -7323,7 +7323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C3:L34"/>
+  <dimension ref="C3:L35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="47.1640625" customWidth="1" style="22" min="6" max="6"/>
@@ -8751,6 +8751,50 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="C35" t="n">
+        <v>32</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0035</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Alif Baa Taa rhyme — PARTIAL 42s (4 safe sections)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gemini Omni Flash x5 clips. Diagnostic first (30cr) proved only 'Alif' mispronounces — Baa/Taa/Saa all verified clean by whisper. Built the four sections without 'Alif': intro+Baa+Taa+Saa+brand tag = 42s. Verse 1, chorus and ending held pending a supplied sung vocal. One re-roll (30cr) because the first Saa clip had Latin alphabet blocks on the floor. Three clips were submitted without the character reference image by mistake — character held, but they gained a green headscarf band the Baa clip lacks.</t>
+        </is>
+      </c>
+      <c r="G35" s="27" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0:42</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>150</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>gemini_omni (Omni Flash)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>productions/0035-alif-baa-taa-full-rhyme-cocomelon-50-60s/00-REQUEST.md</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/costTracker/social-media-tracker.xlsx
+++ b/costTracker/social-media-tracker.xlsx
@@ -8762,12 +8762,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alif Baa Taa rhyme — PARTIAL 42s (4 safe sections)</t>
+          <t>Alif Baa Taa rhyme — 52s (Alif solved)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gemini Omni Flash x5 clips. Diagnostic first (30cr) proved only 'Alif' mispronounces — Baa/Taa/Saa all verified clean by whisper. Built the four sections without 'Alif': intro+Baa+Taa+Saa+brand tag = 42s. Verse 1, chorus and ending held pending a supplied sung vocal. One re-roll (30cr) because the first Saa clip had Latin alphabet blocks on the floor. Three clips were submitted without the character reference image by mistake — character held, but they gained a green headscarf band the Baa clip lacks.</t>
+          <t>Gemini Omni Flash x5 clips. Diagnostic first (30cr) proved only 'Alif' mispronounces — Baa/Taa/Saa all verified clean by whisper. Built the four sections without 'Alif': intro+Baa+Taa+Saa+brand tag = 42s. Verse 1, chorus and ending held pending a supplied sung vocal. One re-roll (30cr) because the first Saa clip had Latin alphabet blocks on the floor. Three clips were submitted without the character reference image by mistake — character held, but they gained a green headscarf band the Baa clip lacks. UPDATE: ALIF SOLVED — having her SPEAK the letter as a call-out over the music instead of singing it produced a correct 'Alif' twice in a row; singing stretches the vowel and that is what broke it. Final cut 52s, intro+Alif+Baa+Taa+Saa+tag, all letters whisper-verified. Latin alphabet blocks recurred through two Alif re-rolls and were removed by a 1.42x crop rather than a third paid attempt.</t>
         </is>
       </c>
       <c r="G35" s="27" t="n">
@@ -8775,14 +8775,14 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0:42</t>
+          <t>0:52</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="J35" t="n">
-        <v>4.95</v>
+        <v>7.92</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
